--- a/InputData/bldgs/EoBSDwEC/Elast of Bldg Svc Demand wrt E Cost.xlsx
+++ b/InputData/bldgs/EoBSDwEC/Elast of Bldg Svc Demand wrt E Cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Dropbox (Energy Innovation)\Desktop\Vensim files from GitHub\EPS US\InputData\bldgs\EoBSDwEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\EoBSDwEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344434C8-6702-4CA8-9A05-280406723E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91471597-66AA-40AF-94F1-F8436CC4A72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30960" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>EoBSDwEC Elasticity of Building Service Demand wrt Energy Cost</t>
   </si>
@@ -118,6 +118,15 @@
   </si>
   <si>
     <t>Commercial Demand Module, Page 12</t>
+  </si>
+  <si>
+    <t>Data Centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. Their demand for computing services is set by the data center load scenarios, not by energy prices, so the service demand elasticity is zero. Price response still works through equipment efficiency (component energy demand elasticity).</t>
   </si>
 </sst>
 </file>
@@ -170,7 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -184,6 +193,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -308,9 +320,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -348,9 +360,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -383,26 +395,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -435,26 +430,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -628,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="65" customWidth="1"/>
@@ -697,29 +675,37 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -771,7 +757,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -779,7 +765,7 @@
     <col min="4" max="4" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>24</v>
       </c>
@@ -792,8 +778,11 @@
       <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -806,8 +795,11 @@
       <c r="D2">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -820,8 +812,11 @@
       <c r="D3">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -834,8 +829,11 @@
       <c r="D4">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -848,8 +846,11 @@
       <c r="D5">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -862,8 +863,11 @@
       <c r="D6">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -876,8 +880,11 @@
       <c r="D7">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -890,8 +897,11 @@
       <c r="D8">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -904,8 +914,11 @@
       <c r="D9">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -918,8 +931,11 @@
       <c r="D10">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -931,6 +947,9 @@
       </c>
       <c r="D11">
         <v>-0.25</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
